--- a/proposal/collaboration/collaboration_merzari.xlsx
+++ b/proposal/collaboration/collaboration_merzari.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eliamerzari/genesis21b/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/misunmin/proj/genesis21b/proposal/collaboration/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4210BC91-A5A9-0542-9DFC-A651799B60FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AADFFF86-B903-D548-BDAE-14198F518286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-280" yWindow="3460" windowWidth="28800" windowHeight="16380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13400" yWindow="5820" windowWidth="28800" windowHeight="16380" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="3" r:id="rId1"/>
@@ -248,235 +248,235 @@
     <t>Tzanio</t>
   </si>
   <si>
-    <t>Penn State</t>
-  </si>
-  <si>
-    <t>Elia Merzari</t>
+    <t>Philippe</t>
+  </si>
+  <si>
+    <t>University of Illinois</t>
+  </si>
+  <si>
+    <t>Idaho National Lab</t>
+  </si>
+  <si>
+    <t>Thomas</t>
+  </si>
+  <si>
+    <t>Novak</t>
+  </si>
+  <si>
+    <t>Lawrence Livermore National Lab</t>
+  </si>
+  <si>
+    <t>Paul</t>
+  </si>
+  <si>
+    <t>Min</t>
+  </si>
+  <si>
+    <t>Merzari</t>
+  </si>
+  <si>
+    <t>Elia</t>
+  </si>
+  <si>
+    <t>Annalisa</t>
+  </si>
+  <si>
+    <t>Younis</t>
+  </si>
+  <si>
+    <t>Rami</t>
+  </si>
+  <si>
+    <t>Virginia Tech</t>
+  </si>
+  <si>
+    <t>Baglietto</t>
+  </si>
+  <si>
+    <t>Emilio</t>
+  </si>
+  <si>
+    <t>Massachusetts Institute of Technology</t>
+  </si>
+  <si>
+    <t>Bardet</t>
+  </si>
+  <si>
+    <t>George Washington University</t>
+  </si>
+  <si>
+    <t>Colombo </t>
+  </si>
+  <si>
+    <t>Emanuela</t>
+  </si>
+  <si>
+    <t>Politecnico di Milano</t>
+  </si>
+  <si>
+    <t>Ferencz</t>
+  </si>
+  <si>
+    <t>Bob</t>
+  </si>
+  <si>
+    <t>Hassan</t>
+  </si>
+  <si>
+    <t>Yassin</t>
+  </si>
+  <si>
+    <t>Texas A&amp;M university</t>
+  </si>
+  <si>
+    <t>Inzoli </t>
+  </si>
+  <si>
+    <t>Fabio </t>
+  </si>
+  <si>
+    <t>Mereu </t>
+  </si>
+  <si>
+    <t>Riccardo</t>
+  </si>
+  <si>
+    <t>Pointer</t>
+  </si>
+  <si>
+    <t>Smith</t>
+  </si>
+  <si>
+    <t>Kord</t>
+  </si>
+  <si>
+    <t>Tavoularis</t>
+  </si>
+  <si>
+    <t>Stavros </t>
+  </si>
+  <si>
+    <t>University of Ottawa</t>
+  </si>
+  <si>
+    <t>Theofilis</t>
+  </si>
+  <si>
+    <t>Vassilios</t>
+  </si>
+  <si>
+    <t>Universidad Politecnica de Madrid</t>
+  </si>
+  <si>
+    <t>Walters</t>
+  </si>
+  <si>
+    <t>Bolotnov</t>
+  </si>
+  <si>
+    <t>Igor</t>
+  </si>
+  <si>
+    <t>Manera</t>
+  </si>
+  <si>
+    <t>University of Michigan</t>
+  </si>
+  <si>
+    <t>Dinh</t>
+  </si>
+  <si>
+    <t>Nam</t>
+  </si>
+  <si>
+    <t>University of Tulsa</t>
+  </si>
+  <si>
+    <t>Ninokata</t>
+  </si>
+  <si>
+    <t>Hisashi</t>
+  </si>
+  <si>
+    <t>Aoki</t>
+  </si>
+  <si>
+    <t>Takayuki </t>
+  </si>
+  <si>
+    <t>Tokyo Institute of Technology</t>
+  </si>
+  <si>
+    <t>Fischer</t>
+  </si>
+  <si>
+    <t>D’Auria</t>
+  </si>
+  <si>
+    <t>Francesco</t>
+  </si>
+  <si>
+    <t>University of Pisa </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sun </t>
+  </si>
+  <si>
+    <t>Xiaodong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siegel </t>
+  </si>
+  <si>
+    <t>Evans</t>
+  </si>
+  <si>
+    <t>Romano</t>
+  </si>
+  <si>
+    <t>April</t>
+  </si>
+  <si>
+    <t>Universiyt of Illinois</t>
+  </si>
+  <si>
+    <t>Keith</t>
+  </si>
+  <si>
+    <t>University of Arkansas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hamilton </t>
+  </si>
+  <si>
+    <t>Steve</t>
+  </si>
+  <si>
+    <t>Gaston</t>
+  </si>
+  <si>
+    <t>Derek</t>
+  </si>
+  <si>
+    <t>Misun</t>
+  </si>
+  <si>
+    <t>Waburton</t>
+  </si>
+  <si>
+    <t>Marin</t>
+  </si>
+  <si>
+    <t>Oana</t>
+  </si>
+  <si>
+    <t>Min, Misun</t>
+  </si>
+  <si>
+    <t>Merari, Elia</t>
   </si>
   <si>
     <t>ebm5351@psu.edu</t>
-  </si>
-  <si>
-    <t>Philippe</t>
-  </si>
-  <si>
-    <t>University of Illinois</t>
-  </si>
-  <si>
-    <t>Idaho National Lab</t>
-  </si>
-  <si>
-    <t>Thomas</t>
-  </si>
-  <si>
-    <t>Novak</t>
-  </si>
-  <si>
-    <t>Lawrence Livermore National Lab</t>
-  </si>
-  <si>
-    <t>Paul</t>
-  </si>
-  <si>
-    <t>Min</t>
-  </si>
-  <si>
-    <t>Merzari</t>
-  </si>
-  <si>
-    <t>Elia</t>
-  </si>
-  <si>
-    <t>Annalisa</t>
-  </si>
-  <si>
-    <t>Younis</t>
-  </si>
-  <si>
-    <t>Rami</t>
-  </si>
-  <si>
-    <t>Virginia Tech</t>
-  </si>
-  <si>
-    <t>Baglietto</t>
-  </si>
-  <si>
-    <t>Emilio</t>
-  </si>
-  <si>
-    <t>Massachusetts Institute of Technology</t>
-  </si>
-  <si>
-    <t>Bardet</t>
-  </si>
-  <si>
-    <t>George Washington University</t>
-  </si>
-  <si>
-    <t>Colombo </t>
-  </si>
-  <si>
-    <t>Emanuela</t>
-  </si>
-  <si>
-    <t>Politecnico di Milano</t>
-  </si>
-  <si>
-    <t>Ferencz</t>
-  </si>
-  <si>
-    <t>Bob</t>
-  </si>
-  <si>
-    <t>Hassan</t>
-  </si>
-  <si>
-    <t>Yassin</t>
-  </si>
-  <si>
-    <t>Texas A&amp;M university</t>
-  </si>
-  <si>
-    <t>Inzoli </t>
-  </si>
-  <si>
-    <t>Fabio </t>
-  </si>
-  <si>
-    <t>Mereu </t>
-  </si>
-  <si>
-    <t>Riccardo</t>
-  </si>
-  <si>
-    <t>Pointer</t>
-  </si>
-  <si>
-    <t>Smith</t>
-  </si>
-  <si>
-    <t>Kord</t>
-  </si>
-  <si>
-    <t>Tavoularis</t>
-  </si>
-  <si>
-    <t>Stavros </t>
-  </si>
-  <si>
-    <t>University of Ottawa</t>
-  </si>
-  <si>
-    <t>Theofilis</t>
-  </si>
-  <si>
-    <t>Vassilios</t>
-  </si>
-  <si>
-    <t>Universidad Politecnica de Madrid</t>
-  </si>
-  <si>
-    <t>Walters</t>
-  </si>
-  <si>
-    <t>Bolotnov</t>
-  </si>
-  <si>
-    <t>Igor</t>
-  </si>
-  <si>
-    <t>Manera</t>
-  </si>
-  <si>
-    <t>University of Michigan</t>
-  </si>
-  <si>
-    <t>Dinh</t>
-  </si>
-  <si>
-    <t>Nam</t>
-  </si>
-  <si>
-    <t>University of Tulsa</t>
-  </si>
-  <si>
-    <t>Ninokata</t>
-  </si>
-  <si>
-    <t>Hisashi</t>
-  </si>
-  <si>
-    <t>Aoki</t>
-  </si>
-  <si>
-    <t>Takayuki </t>
-  </si>
-  <si>
-    <t>Tokyo Institute of Technology</t>
-  </si>
-  <si>
-    <t>Fischer</t>
-  </si>
-  <si>
-    <t>D’Auria</t>
-  </si>
-  <si>
-    <t>Francesco</t>
-  </si>
-  <si>
-    <t>University of Pisa </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sun </t>
-  </si>
-  <si>
-    <t>Xiaodong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siegel </t>
-  </si>
-  <si>
-    <t>Evans</t>
-  </si>
-  <si>
-    <t>Romano</t>
-  </si>
-  <si>
-    <t>April</t>
-  </si>
-  <si>
-    <t>Universiyt of Illinois</t>
-  </si>
-  <si>
-    <t>Keith</t>
-  </si>
-  <si>
-    <t>University of Arkansas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hamilton </t>
-  </si>
-  <si>
-    <t>Steve</t>
-  </si>
-  <si>
-    <t>Gaston</t>
-  </si>
-  <si>
-    <t>Derek</t>
-  </si>
-  <si>
-    <t>Misun</t>
-  </si>
-  <si>
-    <t>Waburton</t>
-  </si>
-  <si>
-    <t>Marin</t>
-  </si>
-  <si>
-    <t>Oana</t>
   </si>
 </sst>
 </file>
@@ -860,19 +860,22 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -881,11 +884,8 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1266,64 +1266,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" s="31"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" s="30"/>
       <c r="E1" s="3"/>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="D2" s="31"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="29" t="s">
+        <v>129</v>
+      </c>
+      <c r="D2" s="30"/>
       <c r="E2" s="3"/>
     </row>
     <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="D3" s="31"/>
+      <c r="B3" s="35"/>
+      <c r="C3" s="29" t="s">
+        <v>130</v>
+      </c>
+      <c r="D3" s="30"/>
       <c r="E3" s="3"/>
     </row>
     <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="27"/>
-      <c r="C4" s="28" t="s">
-        <v>57</v>
-      </c>
-      <c r="D4" s="29"/>
+      <c r="B4" s="35"/>
+      <c r="C4" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="D4" s="32"/>
       <c r="E4" s="3"/>
     </row>
     <row r="5" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="32" t="s">
+      <c r="A6" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="33"/>
-      <c r="C6" s="34" t="str">
+      <c r="B6" s="34"/>
+      <c r="C6" s="27" t="str">
         <f>"Collaborator Table - "&amp;C1&amp;" ("&amp;C2&amp;")"</f>
-        <v>Collaborator Table - Penn State (Elia Merzari)</v>
-      </c>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="34"/>
-      <c r="H6" s="35"/>
+        <v>Collaborator Table - Argonne National Laboratory (Min, Misun)</v>
+      </c>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="28"/>
     </row>
     <row r="7" spans="1:8" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
@@ -1353,20 +1353,20 @@
     </row>
     <row r="8" spans="1:8" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E8" s="23"/>
       <c r="F8" s="23" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G8" s="23" t="s">
         <v>22</v>
@@ -1377,20 +1377,20 @@
     </row>
     <row r="9" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E9" s="25"/>
       <c r="F9" s="25" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G9" s="25" t="s">
         <v>22</v>
@@ -1401,20 +1401,20 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E10" s="23"/>
       <c r="F10" s="23" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G10" s="23" t="s">
         <v>22</v>
@@ -1425,16 +1425,16 @@
     </row>
     <row r="11" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E11" s="25"/>
       <c r="F11" s="25" t="s">
@@ -1449,20 +1449,20 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E12" s="23"/>
       <c r="F12" s="23" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="G12" s="23" t="s">
         <v>22</v>
@@ -1473,20 +1473,20 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D13" s="25" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E13" s="25"/>
       <c r="F13" s="25" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G13" s="25" t="s">
         <v>22</v>
@@ -1497,20 +1497,20 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E14" s="23"/>
       <c r="F14" s="23" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G14" s="23" t="s">
         <v>22</v>
@@ -1521,13 +1521,13 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D15" s="25" t="s">
         <v>46</v>
@@ -1545,20 +1545,20 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E16" s="23"/>
       <c r="F16" s="23" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G16" s="23" t="s">
         <v>22</v>
@@ -1569,20 +1569,20 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C17" s="25" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D17" s="25" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E17" s="25"/>
       <c r="F17" s="25" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G17" s="25" t="s">
         <v>22</v>
@@ -1593,20 +1593,20 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E18" s="23"/>
       <c r="F18" s="23" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G18" s="23" t="s">
         <v>22</v>
@@ -1617,20 +1617,20 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C19" s="25" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D19" s="25" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E19" s="25"/>
       <c r="F19" s="25" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G19" s="25" t="s">
         <v>22</v>
@@ -1641,16 +1641,16 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D20" s="23" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E20" s="23"/>
       <c r="F20" s="23" t="s">
@@ -1665,20 +1665,20 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C21" s="25" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D21" s="25" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E21" s="25"/>
       <c r="F21" s="25" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G21" s="25" t="s">
         <v>22</v>
@@ -1689,16 +1689,16 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D22" s="23" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E22" s="23"/>
       <c r="F22" s="23" t="s">
@@ -1713,20 +1713,20 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C23" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="D23" s="25" t="s">
         <v>67</v>
-      </c>
-      <c r="C23" s="25" t="s">
-        <v>69</v>
-      </c>
-      <c r="D23" s="25" t="s">
-        <v>70</v>
       </c>
       <c r="E23" s="25"/>
       <c r="F23" s="25" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G23" s="25" t="s">
         <v>22</v>
@@ -1737,20 +1737,20 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C24" s="23" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E24" s="23"/>
       <c r="F24" s="23" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G24" s="23" t="s">
         <v>32</v>
@@ -1761,20 +1761,20 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C25" s="25" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D25" s="25" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E25" s="25"/>
       <c r="F25" s="25" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="G25" s="25" t="s">
         <v>32</v>
@@ -1785,20 +1785,20 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C26" s="23" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D26" s="23" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E26" s="23"/>
       <c r="F26" s="23" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G26" s="23" t="s">
         <v>32</v>
@@ -1809,20 +1809,20 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C27" s="25" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D27" s="25" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E27" s="25"/>
       <c r="F27" s="25" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="G27" s="25" t="s">
         <v>27</v>
@@ -1833,20 +1833,20 @@
     </row>
     <row r="28" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D28" s="21" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E28" s="21"/>
       <c r="F28" s="21" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>22</v>
@@ -1857,13 +1857,13 @@
     </row>
     <row r="29" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C29" s="22" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D29" s="21" t="s">
         <v>47</v>
@@ -1881,16 +1881,16 @@
     </row>
     <row r="30" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C30" s="22" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D30" s="21" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E30" s="21"/>
       <c r="F30" s="21" t="s">
@@ -1905,16 +1905,16 @@
     </row>
     <row r="31" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C31" s="22" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D31" s="21" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E31" s="21"/>
       <c r="F31" s="21" t="s">
@@ -1929,20 +1929,20 @@
     </row>
     <row r="32" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C32" s="22" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D32" s="21" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E32" s="21"/>
       <c r="F32" s="21" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G32" s="6" t="s">
         <v>22</v>
@@ -1953,16 +1953,16 @@
     </row>
     <row r="33" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C33" s="22" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D33" s="21" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E33" s="21"/>
       <c r="F33" s="21" t="s">
@@ -1977,20 +1977,20 @@
     </row>
     <row r="34" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C34" s="22" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D34" s="21" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E34" s="21"/>
       <c r="F34" s="21" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>22</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="35" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C35" s="22" t="s">
         <v>53</v>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="E35" s="21"/>
       <c r="F35" s="21" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G35" s="6" t="s">
         <v>22</v>
@@ -2025,16 +2025,16 @@
     </row>
     <row r="36" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C36" s="22" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D36" s="21" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E36" s="21"/>
       <c r="F36" s="21" t="s">
@@ -2049,20 +2049,20 @@
     </row>
     <row r="37" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C37" s="22" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D37" s="21" t="s">
         <v>50</v>
       </c>
       <c r="E37" s="21"/>
       <c r="F37" s="21" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G37" s="6" t="s">
         <v>22</v>
@@ -2073,20 +2073,20 @@
     </row>
     <row r="38" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C38" s="22" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D38" s="21" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E38" s="21"/>
       <c r="F38" s="21" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G38" s="6" t="s">
         <v>22</v>
@@ -3817,21 +3817,21 @@
     </row>
   </sheetData>
   <autoFilter ref="A7:H7" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A8:H7">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A7:H8">
       <sortCondition ref="C7"/>
     </sortState>
   </autoFilter>
   <mergeCells count="10">
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
     <mergeCell ref="C6:H6"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
   </mergeCells>
   <conditionalFormatting sqref="A8:B210">
     <cfRule type="expression" dxfId="7" priority="2">
@@ -3901,64 +3901,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="30" t="s">
+      <c r="B1" s="35"/>
+      <c r="C1" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="31"/>
+      <c r="D1" s="30"/>
       <c r="E1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="30" t="s">
+      <c r="B2" s="35"/>
+      <c r="C2" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="31"/>
+      <c r="D2" s="30"/>
       <c r="E2" s="3"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="30" t="s">
+      <c r="B3" s="35"/>
+      <c r="C3" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="31"/>
+      <c r="D3" s="30"/>
       <c r="E3" s="3"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="27"/>
-      <c r="C4" s="30" t="s">
+      <c r="B4" s="35"/>
+      <c r="C4" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="31"/>
+      <c r="D4" s="30"/>
       <c r="E4" s="3"/>
     </row>
     <row r="5" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="32" t="s">
+      <c r="A6" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="33"/>
-      <c r="C6" s="34" t="str">
+      <c r="B6" s="34"/>
+      <c r="C6" s="27" t="str">
         <f>"Collaborator Table - "&amp;C1&amp;" ("&amp;C2&amp;")"</f>
         <v>Collaborator Table - University of XYZ (Jones, Jane)</v>
       </c>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="34"/>
-      <c r="H6" s="35"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="28"/>
     </row>
     <row r="7" spans="1:8" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
@@ -8185,6 +8185,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001733C14AC8EC6F498F123411DB8BC020" ma:contentTypeVersion="2" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c1f196d61ef494b6c4f62f58be5bb14e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7b7cc8fe-90e2-43f3-ad3c-00f457ec8258" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="46c76a5a58717c3453de3c52cd271f55" ns2:_="">
     <xsd:import namespace="7b7cc8fe-90e2-43f3-ad3c-00f457ec8258"/>
@@ -8316,12 +8322,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -8332,6 +8332,15 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7ACA6411-41A0-4B6C-874D-1FC05CC4B568}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE70D9AC-1270-4AD5-BB63-23D2B0A32B51}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8349,15 +8358,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7ACA6411-41A0-4B6C-874D-1FC05CC4B568}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53ACD002-FFBE-4185-9DDB-0AA3A824C3C1}">
   <ds:schemaRefs>
